--- a/Codigos de ORFEO de las ventanillas correspondencia y Mesas de Control.xlsx
+++ b/Codigos de ORFEO de las ventanillas correspondencia y Mesas de Control.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\maalvare\OneDrive - Fiscalia General de la Nacion\VICTIMAS\AÑO 2022\VICTIMAS\SGI\MESA CREACIÓN NC\2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyecto TICs\Nuevo Enlace\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619E0723-6E93-492C-9D77-7E7D4C927959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315" activeTab="1"/>
+    <workbookView xWindow="4812" yWindow="108" windowWidth="13236" windowHeight="13224" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ventanillas" sheetId="1" r:id="rId1"/>
@@ -222,7 +223,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -569,16 +570,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A2:B34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="3"/>
-    <col min="2" max="2" width="87.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="3"/>
+    <col min="2" max="2" width="87.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
@@ -586,7 +587,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -594,7 +595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -602,7 +603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -610,7 +611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -618,7 +619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -626,7 +627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -634,7 +635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -642,7 +643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -650,7 +651,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -658,7 +659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -666,7 +667,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -674,7 +675,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -682,7 +683,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -690,7 +691,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -698,7 +699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -706,7 +707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -714,7 +715,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -722,7 +723,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -730,7 +731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -738,7 +739,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -746,7 +747,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -754,7 +755,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -762,7 +763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -770,7 +771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -778,7 +779,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -786,7 +787,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -794,7 +795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -802,7 +803,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -810,7 +811,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -818,7 +819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -826,7 +827,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -834,7 +835,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -848,15 +849,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A3:C32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>32</v>
       </c>
@@ -867,7 +868,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>23</v>
       </c>
@@ -878,7 +879,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>21</v>
       </c>
@@ -889,7 +890,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>24</v>
       </c>
@@ -900,7 +901,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>11</v>
       </c>
@@ -911,7 +912,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>15</v>
       </c>
@@ -922,7 +923,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -933,7 +934,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>26</v>
       </c>
@@ -944,7 +945,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>5</v>
       </c>
@@ -955,7 +956,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>7</v>
       </c>
@@ -966,7 +967,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -977,7 +978,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -988,7 +989,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>8</v>
       </c>
@@ -999,7 +1000,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>22</v>
       </c>
@@ -1010,7 +1011,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -1021,7 +1022,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1032,7 +1033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1043,7 +1044,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>9</v>
       </c>
@@ -1054,7 +1055,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>29</v>
       </c>
@@ -1065,7 +1066,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -1076,7 +1077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -1087,7 +1088,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>17</v>
       </c>
@@ -1098,7 +1099,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>25</v>
       </c>
@@ -1109,7 +1110,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -1120,7 +1121,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>28</v>
       </c>
@@ -1131,7 +1132,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -1142,7 +1143,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>19</v>
       </c>
@@ -1164,7 +1165,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>12</v>
       </c>
@@ -1175,7 +1176,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>14</v>
       </c>
@@ -1187,7 +1188,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A4:C32">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:C32">
     <sortCondition ref="C4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
